--- a/inst/extdata/DBSetupV2.xlsx
+++ b/inst/extdata/DBSetupV2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e282219\Downloads\github\repoquet\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E340D56-26E2-493C-AED0-E41270AA4072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D407A6-E3AF-4545-817E-005B74E59D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="12790" windowHeight="9740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5320" yWindow="2340" windowWidth="30940" windowHeight="16950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3402" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3388" uniqueCount="594">
   <si>
     <t>Database</t>
   </si>
@@ -523,9 +523,6 @@
     <t>2016</t>
   </si>
   <si>
-    <t>TQP 2016/PUF_AISDES_TQP_2016.csv</t>
-  </si>
-  <si>
     <t>TQP 2016/PUF_AISPCODE_TQP_2016.csv</t>
   </si>
   <si>
@@ -1142,9 +1139,6 @@
   </si>
   <si>
     <t>Adult TQIP PUF AY 2010-2016/TQIP PUF AY 2015/CSV/TQIP_RDS_VITALS.csv</t>
-  </si>
-  <si>
-    <t>Adult TQIP PUF AY 2010-2016/TQIP PUF AY 2016/CSV/TQIP_RDS_AISDES.csv</t>
   </si>
   <si>
     <t>Adult TQIP PUF AY 2010-2016/TQIP PUF AY 2016/CSV/TQIP_RDS_AISPCODE.csv</t>
@@ -2090,7 +2084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G486"/>
+  <dimension ref="A1:G484"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4504,7 +4498,7 @@
         <v>167</v>
       </c>
       <c r="D105" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E105" t="s">
         <v>11</v>
@@ -4527,7 +4521,7 @@
         <v>168</v>
       </c>
       <c r="D106" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E106" t="s">
         <v>11</v>
@@ -4550,7 +4544,7 @@
         <v>169</v>
       </c>
       <c r="D107" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E107" t="s">
         <v>11</v>
@@ -4573,7 +4567,7 @@
         <v>170</v>
       </c>
       <c r="D108" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E108" t="s">
         <v>11</v>
@@ -4596,7 +4590,7 @@
         <v>171</v>
       </c>
       <c r="D109" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E109" t="s">
         <v>11</v>
@@ -4619,7 +4613,7 @@
         <v>172</v>
       </c>
       <c r="D110" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E110" t="s">
         <v>11</v>
@@ -4642,7 +4636,7 @@
         <v>173</v>
       </c>
       <c r="D111" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E111" t="s">
         <v>11</v>
@@ -4665,7 +4659,7 @@
         <v>174</v>
       </c>
       <c r="D112" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E112" t="s">
         <v>11</v>
@@ -4688,7 +4682,7 @@
         <v>175</v>
       </c>
       <c r="D113" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E113" t="s">
         <v>11</v>
@@ -4711,7 +4705,7 @@
         <v>176</v>
       </c>
       <c r="D114" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E114" t="s">
         <v>11</v>
@@ -4734,7 +4728,7 @@
         <v>177</v>
       </c>
       <c r="D115" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E115" t="s">
         <v>11</v>
@@ -4757,7 +4751,7 @@
         <v>178</v>
       </c>
       <c r="D116" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E116" t="s">
         <v>11</v>
@@ -4780,7 +4774,7 @@
         <v>179</v>
       </c>
       <c r="D117" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E117" t="s">
         <v>11</v>
@@ -4803,7 +4797,7 @@
         <v>180</v>
       </c>
       <c r="D118" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E118" t="s">
         <v>11</v>
@@ -4826,7 +4820,7 @@
         <v>181</v>
       </c>
       <c r="D119" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E119" t="s">
         <v>11</v>
@@ -4849,7 +4843,7 @@
         <v>182</v>
       </c>
       <c r="D120" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E120" t="s">
         <v>11</v>
@@ -4872,7 +4866,7 @@
         <v>183</v>
       </c>
       <c r="D121" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E121" t="s">
         <v>11</v>
@@ -4895,7 +4889,7 @@
         <v>184</v>
       </c>
       <c r="D122" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E122" t="s">
         <v>11</v>
@@ -4918,7 +4912,7 @@
         <v>185</v>
       </c>
       <c r="D123" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E123" t="s">
         <v>11</v>
@@ -4941,7 +4935,7 @@
         <v>186</v>
       </c>
       <c r="D124" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E124" t="s">
         <v>11</v>
@@ -4964,7 +4958,7 @@
         <v>187</v>
       </c>
       <c r="D125" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E125" t="s">
         <v>11</v>
@@ -4987,7 +4981,7 @@
         <v>188</v>
       </c>
       <c r="D126" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E126" t="s">
         <v>11</v>
@@ -5010,7 +5004,7 @@
         <v>189</v>
       </c>
       <c r="D127" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="E127" t="s">
         <v>11</v>
@@ -5030,10 +5024,10 @@
         <v>8</v>
       </c>
       <c r="C128" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D128" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="E128" t="s">
         <v>11</v>
@@ -5056,7 +5050,7 @@
         <v>192</v>
       </c>
       <c r="D129" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E129" t="s">
         <v>11</v>
@@ -5079,7 +5073,7 @@
         <v>193</v>
       </c>
       <c r="D130" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E130" t="s">
         <v>11</v>
@@ -5102,7 +5096,7 @@
         <v>194</v>
       </c>
       <c r="D131" t="s">
-        <v>162</v>
+        <v>39</v>
       </c>
       <c r="E131" t="s">
         <v>11</v>
@@ -5125,7 +5119,7 @@
         <v>195</v>
       </c>
       <c r="D132" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="E132" t="s">
         <v>11</v>
@@ -5134,7 +5128,7 @@
         <v>12</v>
       </c>
       <c r="G132" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5145,19 +5139,19 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
+        <v>197</v>
+      </c>
+      <c r="D133" t="s">
+        <v>19</v>
+      </c>
+      <c r="E133" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G133" t="s">
         <v>196</v>
-      </c>
-      <c r="D133" t="s">
-        <v>165</v>
-      </c>
-      <c r="E133" t="s">
-        <v>11</v>
-      </c>
-      <c r="F133" t="s">
-        <v>12</v>
-      </c>
-      <c r="G133" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5171,7 +5165,7 @@
         <v>198</v>
       </c>
       <c r="D134" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E134" t="s">
         <v>11</v>
@@ -5180,7 +5174,7 @@
         <v>12</v>
       </c>
       <c r="G134" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5194,7 +5188,7 @@
         <v>199</v>
       </c>
       <c r="D135" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E135" t="s">
         <v>11</v>
@@ -5203,7 +5197,7 @@
         <v>12</v>
       </c>
       <c r="G135" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5217,7 +5211,7 @@
         <v>200</v>
       </c>
       <c r="D136" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E136" t="s">
         <v>11</v>
@@ -5226,7 +5220,7 @@
         <v>12</v>
       </c>
       <c r="G136" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5240,7 +5234,7 @@
         <v>201</v>
       </c>
       <c r="D137" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E137" t="s">
         <v>11</v>
@@ -5249,7 +5243,7 @@
         <v>12</v>
       </c>
       <c r="G137" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5263,7 +5257,7 @@
         <v>202</v>
       </c>
       <c r="D138" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E138" t="s">
         <v>11</v>
@@ -5272,7 +5266,7 @@
         <v>12</v>
       </c>
       <c r="G138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5286,7 +5280,7 @@
         <v>203</v>
       </c>
       <c r="D139" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E139" t="s">
         <v>11</v>
@@ -5295,7 +5289,7 @@
         <v>12</v>
       </c>
       <c r="G139" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5309,7 +5303,7 @@
         <v>204</v>
       </c>
       <c r="D140" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E140" t="s">
         <v>11</v>
@@ -5318,7 +5312,7 @@
         <v>12</v>
       </c>
       <c r="G140" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5332,7 +5326,7 @@
         <v>205</v>
       </c>
       <c r="D141" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E141" t="s">
         <v>11</v>
@@ -5341,7 +5335,7 @@
         <v>12</v>
       </c>
       <c r="G141" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5355,7 +5349,7 @@
         <v>206</v>
       </c>
       <c r="D142" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E142" t="s">
         <v>11</v>
@@ -5364,7 +5358,7 @@
         <v>12</v>
       </c>
       <c r="G142" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5378,7 +5372,7 @@
         <v>207</v>
       </c>
       <c r="D143" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="E143" t="s">
         <v>11</v>
@@ -5387,7 +5381,7 @@
         <v>12</v>
       </c>
       <c r="G143" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5398,19 +5392,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
+        <v>209</v>
+      </c>
+      <c r="D144" t="s">
+        <v>19</v>
+      </c>
+      <c r="E144" t="s">
+        <v>11</v>
+      </c>
+      <c r="F144" t="s">
+        <v>12</v>
+      </c>
+      <c r="G144" t="s">
         <v>208</v>
-      </c>
-      <c r="D144" t="s">
-        <v>165</v>
-      </c>
-      <c r="E144" t="s">
-        <v>11</v>
-      </c>
-      <c r="F144" t="s">
-        <v>12</v>
-      </c>
-      <c r="G144" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5424,7 +5418,7 @@
         <v>210</v>
       </c>
       <c r="D145" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E145" t="s">
         <v>11</v>
@@ -5433,7 +5427,7 @@
         <v>12</v>
       </c>
       <c r="G145" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5447,7 +5441,7 @@
         <v>211</v>
       </c>
       <c r="D146" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E146" t="s">
         <v>11</v>
@@ -5456,7 +5450,7 @@
         <v>12</v>
       </c>
       <c r="G146" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5470,7 +5464,7 @@
         <v>212</v>
       </c>
       <c r="D147" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E147" t="s">
         <v>11</v>
@@ -5479,7 +5473,7 @@
         <v>12</v>
       </c>
       <c r="G147" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5493,7 +5487,7 @@
         <v>213</v>
       </c>
       <c r="D148" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E148" t="s">
         <v>11</v>
@@ -5502,7 +5496,7 @@
         <v>12</v>
       </c>
       <c r="G148" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5516,7 +5510,7 @@
         <v>214</v>
       </c>
       <c r="D149" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E149" t="s">
         <v>11</v>
@@ -5525,7 +5519,7 @@
         <v>12</v>
       </c>
       <c r="G149" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5539,7 +5533,7 @@
         <v>215</v>
       </c>
       <c r="D150" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E150" t="s">
         <v>11</v>
@@ -5548,7 +5542,7 @@
         <v>12</v>
       </c>
       <c r="G150" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5562,7 +5556,7 @@
         <v>216</v>
       </c>
       <c r="D151" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E151" t="s">
         <v>11</v>
@@ -5571,7 +5565,7 @@
         <v>12</v>
       </c>
       <c r="G151" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5585,7 +5579,7 @@
         <v>217</v>
       </c>
       <c r="D152" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E152" t="s">
         <v>11</v>
@@ -5594,7 +5588,7 @@
         <v>12</v>
       </c>
       <c r="G152" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5608,7 +5602,7 @@
         <v>218</v>
       </c>
       <c r="D153" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E153" t="s">
         <v>11</v>
@@ -5617,7 +5611,7 @@
         <v>12</v>
       </c>
       <c r="G153" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5631,7 +5625,7 @@
         <v>219</v>
       </c>
       <c r="D154" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E154" t="s">
         <v>11</v>
@@ -5640,7 +5634,7 @@
         <v>12</v>
       </c>
       <c r="G154" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5651,19 +5645,19 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
+        <v>221</v>
+      </c>
+      <c r="D155" t="s">
+        <v>165</v>
+      </c>
+      <c r="E155" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155" t="s">
+        <v>12</v>
+      </c>
+      <c r="G155" t="s">
         <v>220</v>
-      </c>
-      <c r="D155" t="s">
-        <v>10</v>
-      </c>
-      <c r="E155" t="s">
-        <v>11</v>
-      </c>
-      <c r="F155" t="s">
-        <v>12</v>
-      </c>
-      <c r="G155" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5677,7 +5671,7 @@
         <v>222</v>
       </c>
       <c r="D156" t="s">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="E156" t="s">
         <v>11</v>
@@ -5686,7 +5680,7 @@
         <v>12</v>
       </c>
       <c r="G156" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5700,7 +5694,7 @@
         <v>223</v>
       </c>
       <c r="D157" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E157" t="s">
         <v>11</v>
@@ -5709,7 +5703,7 @@
         <v>12</v>
       </c>
       <c r="G157" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5723,7 +5717,7 @@
         <v>224</v>
       </c>
       <c r="D158" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E158" t="s">
         <v>11</v>
@@ -5732,7 +5726,7 @@
         <v>12</v>
       </c>
       <c r="G158" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5746,7 +5740,7 @@
         <v>225</v>
       </c>
       <c r="D159" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E159" t="s">
         <v>11</v>
@@ -5755,7 +5749,7 @@
         <v>12</v>
       </c>
       <c r="G159" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5769,7 +5763,7 @@
         <v>226</v>
       </c>
       <c r="D160" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E160" t="s">
         <v>11</v>
@@ -5778,7 +5772,7 @@
         <v>12</v>
       </c>
       <c r="G160" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5792,7 +5786,7 @@
         <v>227</v>
       </c>
       <c r="D161" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E161" t="s">
         <v>11</v>
@@ -5801,7 +5795,7 @@
         <v>12</v>
       </c>
       <c r="G161" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5815,7 +5809,7 @@
         <v>228</v>
       </c>
       <c r="D162" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E162" t="s">
         <v>11</v>
@@ -5824,7 +5818,7 @@
         <v>12</v>
       </c>
       <c r="G162" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5838,7 +5832,7 @@
         <v>229</v>
       </c>
       <c r="D163" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E163" t="s">
         <v>11</v>
@@ -5847,7 +5841,7 @@
         <v>12</v>
       </c>
       <c r="G163" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5861,7 +5855,7 @@
         <v>230</v>
       </c>
       <c r="D164" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E164" t="s">
         <v>11</v>
@@ -5870,7 +5864,7 @@
         <v>12</v>
       </c>
       <c r="G164" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5884,7 +5878,7 @@
         <v>231</v>
       </c>
       <c r="D165" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E165" t="s">
         <v>11</v>
@@ -5893,7 +5887,7 @@
         <v>12</v>
       </c>
       <c r="G165" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5907,7 +5901,7 @@
         <v>232</v>
       </c>
       <c r="D166" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E166" t="s">
         <v>11</v>
@@ -5916,7 +5910,7 @@
         <v>12</v>
       </c>
       <c r="G166" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5930,7 +5924,7 @@
         <v>233</v>
       </c>
       <c r="D167" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E167" t="s">
         <v>11</v>
@@ -5939,21 +5933,21 @@
         <v>12</v>
       </c>
       <c r="G167" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B168" t="s">
-        <v>8</v>
+        <v>235</v>
       </c>
       <c r="C168" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D168" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="E168" t="s">
         <v>11</v>
@@ -5962,44 +5956,44 @@
         <v>12</v>
       </c>
       <c r="G168" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B169" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C169" t="s">
+        <v>238</v>
+      </c>
+      <c r="D169" t="s">
+        <v>106</v>
+      </c>
+      <c r="E169" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" t="s">
+        <v>12</v>
+      </c>
+      <c r="G169" t="s">
         <v>237</v>
-      </c>
-      <c r="D169" t="s">
-        <v>103</v>
-      </c>
-      <c r="E169" t="s">
-        <v>11</v>
-      </c>
-      <c r="F169" t="s">
-        <v>12</v>
-      </c>
-      <c r="G169" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B170" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C170" t="s">
         <v>239</v>
       </c>
       <c r="D170" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E170" t="s">
         <v>11</v>
@@ -6008,21 +6002,21 @@
         <v>12</v>
       </c>
       <c r="G170" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B171" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C171" t="s">
         <v>240</v>
       </c>
       <c r="D171" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E171" t="s">
         <v>11</v>
@@ -6031,21 +6025,21 @@
         <v>12</v>
       </c>
       <c r="G171" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B172" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C172" t="s">
         <v>241</v>
       </c>
       <c r="D172" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E172" t="s">
         <v>11</v>
@@ -6054,21 +6048,21 @@
         <v>12</v>
       </c>
       <c r="G172" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B173" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C173" t="s">
         <v>242</v>
       </c>
       <c r="D173" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E173" t="s">
         <v>11</v>
@@ -6077,21 +6071,21 @@
         <v>12</v>
       </c>
       <c r="G173" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B174" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C174" t="s">
         <v>243</v>
       </c>
       <c r="D174" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E174" t="s">
         <v>11</v>
@@ -6100,21 +6094,21 @@
         <v>12</v>
       </c>
       <c r="G174" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B175" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C175" t="s">
         <v>244</v>
       </c>
       <c r="D175" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E175" t="s">
         <v>11</v>
@@ -6123,21 +6117,21 @@
         <v>12</v>
       </c>
       <c r="G175" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B176" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C176" t="s">
         <v>245</v>
       </c>
       <c r="D176" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E176" t="s">
         <v>11</v>
@@ -6146,21 +6140,21 @@
         <v>12</v>
       </c>
       <c r="G176" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B177" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C177" t="s">
         <v>246</v>
       </c>
       <c r="D177" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E177" t="s">
         <v>11</v>
@@ -6169,21 +6163,21 @@
         <v>12</v>
       </c>
       <c r="G177" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B178" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C178" t="s">
         <v>247</v>
       </c>
       <c r="D178" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E178" t="s">
         <v>11</v>
@@ -6192,21 +6186,21 @@
         <v>12</v>
       </c>
       <c r="G178" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B179" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C179" t="s">
         <v>248</v>
       </c>
       <c r="D179" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E179" t="s">
         <v>11</v>
@@ -6215,21 +6209,21 @@
         <v>12</v>
       </c>
       <c r="G179" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B180" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C180" t="s">
         <v>249</v>
       </c>
       <c r="D180" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E180" t="s">
         <v>11</v>
@@ -6238,21 +6232,21 @@
         <v>12</v>
       </c>
       <c r="G180" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B181" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C181" t="s">
         <v>250</v>
       </c>
       <c r="D181" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E181" t="s">
         <v>11</v>
@@ -6261,21 +6255,21 @@
         <v>12</v>
       </c>
       <c r="G181" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B182" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C182" t="s">
         <v>251</v>
       </c>
       <c r="D182" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E182" t="s">
         <v>11</v>
@@ -6284,21 +6278,21 @@
         <v>12</v>
       </c>
       <c r="G182" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B183" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C183" t="s">
         <v>252</v>
       </c>
       <c r="D183" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E183" t="s">
         <v>11</v>
@@ -6307,21 +6301,21 @@
         <v>12</v>
       </c>
       <c r="G183" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B184" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C184" t="s">
         <v>253</v>
       </c>
       <c r="D184" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E184" t="s">
         <v>11</v>
@@ -6330,21 +6324,21 @@
         <v>12</v>
       </c>
       <c r="G184" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B185" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C185" t="s">
         <v>254</v>
       </c>
       <c r="D185" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E185" t="s">
         <v>11</v>
@@ -6353,21 +6347,21 @@
         <v>12</v>
       </c>
       <c r="G185" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B186" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C186" t="s">
         <v>255</v>
       </c>
       <c r="D186" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E186" t="s">
         <v>11</v>
@@ -6376,21 +6370,21 @@
         <v>12</v>
       </c>
       <c r="G186" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B187" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C187" t="s">
         <v>256</v>
       </c>
       <c r="D187" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="E187" t="s">
         <v>11</v>
@@ -6399,44 +6393,44 @@
         <v>12</v>
       </c>
       <c r="G187" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B188" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C188" t="s">
+        <v>258</v>
+      </c>
+      <c r="D188" t="s">
+        <v>106</v>
+      </c>
+      <c r="E188" t="s">
+        <v>11</v>
+      </c>
+      <c r="F188" t="s">
+        <v>12</v>
+      </c>
+      <c r="G188" t="s">
         <v>257</v>
-      </c>
-      <c r="D188" t="s">
-        <v>103</v>
-      </c>
-      <c r="E188" t="s">
-        <v>11</v>
-      </c>
-      <c r="F188" t="s">
-        <v>12</v>
-      </c>
-      <c r="G188" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B189" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C189" t="s">
         <v>259</v>
       </c>
       <c r="D189" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E189" t="s">
         <v>11</v>
@@ -6445,21 +6439,21 @@
         <v>12</v>
       </c>
       <c r="G189" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B190" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C190" t="s">
         <v>260</v>
       </c>
       <c r="D190" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E190" t="s">
         <v>11</v>
@@ -6468,21 +6462,21 @@
         <v>12</v>
       </c>
       <c r="G190" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B191" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C191" t="s">
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E191" t="s">
         <v>11</v>
@@ -6491,21 +6485,21 @@
         <v>12</v>
       </c>
       <c r="G191" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B192" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C192" t="s">
         <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E192" t="s">
         <v>11</v>
@@ -6514,21 +6508,21 @@
         <v>12</v>
       </c>
       <c r="G192" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B193" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C193" t="s">
         <v>263</v>
       </c>
       <c r="D193" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E193" t="s">
         <v>11</v>
@@ -6537,21 +6531,21 @@
         <v>12</v>
       </c>
       <c r="G193" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B194" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C194" t="s">
         <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E194" t="s">
         <v>11</v>
@@ -6560,21 +6554,21 @@
         <v>12</v>
       </c>
       <c r="G194" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B195" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C195" t="s">
         <v>265</v>
       </c>
       <c r="D195" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E195" t="s">
         <v>11</v>
@@ -6583,21 +6577,21 @@
         <v>12</v>
       </c>
       <c r="G195" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B196" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C196" t="s">
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E196" t="s">
         <v>11</v>
@@ -6606,21 +6600,21 @@
         <v>12</v>
       </c>
       <c r="G196" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B197" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C197" t="s">
         <v>267</v>
       </c>
       <c r="D197" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E197" t="s">
         <v>11</v>
@@ -6629,21 +6623,21 @@
         <v>12</v>
       </c>
       <c r="G197" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B198" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C198" t="s">
         <v>268</v>
       </c>
       <c r="D198" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E198" t="s">
         <v>11</v>
@@ -6652,21 +6646,21 @@
         <v>12</v>
       </c>
       <c r="G198" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B199" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C199" t="s">
         <v>269</v>
       </c>
       <c r="D199" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E199" t="s">
         <v>11</v>
@@ -6675,21 +6669,21 @@
         <v>12</v>
       </c>
       <c r="G199" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B200" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C200" t="s">
         <v>270</v>
       </c>
       <c r="D200" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E200" t="s">
         <v>11</v>
@@ -6698,21 +6692,21 @@
         <v>12</v>
       </c>
       <c r="G200" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B201" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C201" t="s">
         <v>271</v>
       </c>
       <c r="D201" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E201" t="s">
         <v>11</v>
@@ -6721,21 +6715,21 @@
         <v>12</v>
       </c>
       <c r="G201" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B202" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C202" t="s">
         <v>272</v>
       </c>
       <c r="D202" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E202" t="s">
         <v>11</v>
@@ -6744,21 +6738,21 @@
         <v>12</v>
       </c>
       <c r="G202" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B203" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C203" t="s">
         <v>273</v>
       </c>
       <c r="D203" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E203" t="s">
         <v>11</v>
@@ -6767,21 +6761,21 @@
         <v>12</v>
       </c>
       <c r="G203" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B204" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C204" t="s">
         <v>274</v>
       </c>
       <c r="D204" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E204" t="s">
         <v>11</v>
@@ -6790,21 +6784,21 @@
         <v>12</v>
       </c>
       <c r="G204" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B205" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C205" t="s">
         <v>275</v>
       </c>
       <c r="D205" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E205" t="s">
         <v>11</v>
@@ -6813,21 +6807,21 @@
         <v>12</v>
       </c>
       <c r="G205" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B206" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C206" t="s">
         <v>276</v>
       </c>
       <c r="D206" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="E206" t="s">
         <v>11</v>
@@ -6836,44 +6830,44 @@
         <v>12</v>
       </c>
       <c r="G206" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B207" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C207" t="s">
+        <v>278</v>
+      </c>
+      <c r="D207" t="s">
+        <v>106</v>
+      </c>
+      <c r="E207" t="s">
+        <v>11</v>
+      </c>
+      <c r="F207" t="s">
+        <v>12</v>
+      </c>
+      <c r="G207" t="s">
         <v>277</v>
-      </c>
-      <c r="D207" t="s">
-        <v>103</v>
-      </c>
-      <c r="E207" t="s">
-        <v>11</v>
-      </c>
-      <c r="F207" t="s">
-        <v>12</v>
-      </c>
-      <c r="G207" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B208" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C208" t="s">
         <v>279</v>
       </c>
       <c r="D208" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E208" t="s">
         <v>11</v>
@@ -6882,21 +6876,21 @@
         <v>12</v>
       </c>
       <c r="G208" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B209" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C209" t="s">
         <v>280</v>
       </c>
       <c r="D209" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E209" t="s">
         <v>11</v>
@@ -6905,21 +6899,21 @@
         <v>12</v>
       </c>
       <c r="G209" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B210" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C210" t="s">
         <v>281</v>
       </c>
       <c r="D210" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E210" t="s">
         <v>11</v>
@@ -6928,21 +6922,21 @@
         <v>12</v>
       </c>
       <c r="G210" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B211" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C211" t="s">
         <v>282</v>
       </c>
       <c r="D211" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E211" t="s">
         <v>11</v>
@@ -6951,21 +6945,21 @@
         <v>12</v>
       </c>
       <c r="G211" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B212" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C212" t="s">
         <v>283</v>
       </c>
       <c r="D212" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E212" t="s">
         <v>11</v>
@@ -6974,21 +6968,21 @@
         <v>12</v>
       </c>
       <c r="G212" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B213" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C213" t="s">
         <v>284</v>
       </c>
       <c r="D213" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E213" t="s">
         <v>11</v>
@@ -6997,21 +6991,21 @@
         <v>12</v>
       </c>
       <c r="G213" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B214" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C214" t="s">
         <v>285</v>
       </c>
       <c r="D214" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E214" t="s">
         <v>11</v>
@@ -7020,21 +7014,21 @@
         <v>12</v>
       </c>
       <c r="G214" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B215" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C215" t="s">
         <v>286</v>
       </c>
       <c r="D215" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E215" t="s">
         <v>11</v>
@@ -7043,21 +7037,21 @@
         <v>12</v>
       </c>
       <c r="G215" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B216" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C216" t="s">
         <v>287</v>
       </c>
       <c r="D216" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E216" t="s">
         <v>11</v>
@@ -7066,21 +7060,21 @@
         <v>12</v>
       </c>
       <c r="G216" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B217" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C217" t="s">
         <v>288</v>
       </c>
       <c r="D217" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E217" t="s">
         <v>11</v>
@@ -7089,21 +7083,21 @@
         <v>12</v>
       </c>
       <c r="G217" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B218" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C218" t="s">
         <v>289</v>
       </c>
       <c r="D218" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E218" t="s">
         <v>11</v>
@@ -7112,21 +7106,21 @@
         <v>12</v>
       </c>
       <c r="G218" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="219" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B219" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C219" t="s">
         <v>290</v>
       </c>
       <c r="D219" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E219" t="s">
         <v>11</v>
@@ -7135,21 +7129,21 @@
         <v>12</v>
       </c>
       <c r="G219" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="220" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B220" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C220" t="s">
         <v>291</v>
       </c>
       <c r="D220" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E220" t="s">
         <v>11</v>
@@ -7158,21 +7152,21 @@
         <v>12</v>
       </c>
       <c r="G220" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="221" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B221" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C221" t="s">
         <v>292</v>
       </c>
       <c r="D221" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E221" t="s">
         <v>11</v>
@@ -7181,21 +7175,21 @@
         <v>12</v>
       </c>
       <c r="G221" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B222" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C222" t="s">
         <v>293</v>
       </c>
       <c r="D222" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E222" t="s">
         <v>11</v>
@@ -7204,21 +7198,21 @@
         <v>12</v>
       </c>
       <c r="G222" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="223" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B223" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C223" t="s">
         <v>294</v>
       </c>
       <c r="D223" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E223" t="s">
         <v>11</v>
@@ -7227,21 +7221,21 @@
         <v>12</v>
       </c>
       <c r="G223" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="224" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B224" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C224" t="s">
         <v>295</v>
       </c>
       <c r="D224" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="E224" t="s">
         <v>11</v>
@@ -7250,44 +7244,44 @@
         <v>12</v>
       </c>
       <c r="G224" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
     </row>
     <row r="225" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B225" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C225" t="s">
+        <v>297</v>
+      </c>
+      <c r="D225" t="s">
+        <v>106</v>
+      </c>
+      <c r="E225" t="s">
+        <v>11</v>
+      </c>
+      <c r="F225" t="s">
+        <v>12</v>
+      </c>
+      <c r="G225" t="s">
         <v>296</v>
-      </c>
-      <c r="D225" t="s">
-        <v>103</v>
-      </c>
-      <c r="E225" t="s">
-        <v>11</v>
-      </c>
-      <c r="F225" t="s">
-        <v>12</v>
-      </c>
-      <c r="G225" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B226" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C226" t="s">
         <v>298</v>
       </c>
       <c r="D226" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E226" t="s">
         <v>11</v>
@@ -7296,21 +7290,21 @@
         <v>12</v>
       </c>
       <c r="G226" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="227" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B227" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C227" t="s">
         <v>299</v>
       </c>
       <c r="D227" t="s">
-        <v>112</v>
+        <v>300</v>
       </c>
       <c r="E227" t="s">
         <v>11</v>
@@ -7319,21 +7313,21 @@
         <v>12</v>
       </c>
       <c r="G227" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="228" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B228" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C228" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D228" t="s">
-        <v>301</v>
+        <v>114</v>
       </c>
       <c r="E228" t="s">
         <v>11</v>
@@ -7342,21 +7336,21 @@
         <v>12</v>
       </c>
       <c r="G228" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="229" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B229" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C229" t="s">
         <v>302</v>
       </c>
       <c r="D229" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E229" t="s">
         <v>11</v>
@@ -7365,21 +7359,21 @@
         <v>12</v>
       </c>
       <c r="G229" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="230" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B230" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C230" t="s">
         <v>303</v>
       </c>
       <c r="D230" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E230" t="s">
         <v>11</v>
@@ -7388,21 +7382,21 @@
         <v>12</v>
       </c>
       <c r="G230" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="231" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B231" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C231" t="s">
         <v>304</v>
       </c>
       <c r="D231" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E231" t="s">
         <v>11</v>
@@ -7411,21 +7405,21 @@
         <v>12</v>
       </c>
       <c r="G231" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="232" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B232" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C232" t="s">
         <v>305</v>
       </c>
       <c r="D232" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E232" t="s">
         <v>11</v>
@@ -7434,21 +7428,21 @@
         <v>12</v>
       </c>
       <c r="G232" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="233" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B233" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C233" t="s">
         <v>306</v>
       </c>
       <c r="D233" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E233" t="s">
         <v>11</v>
@@ -7457,21 +7451,21 @@
         <v>12</v>
       </c>
       <c r="G233" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B234" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C234" t="s">
         <v>307</v>
       </c>
       <c r="D234" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E234" t="s">
         <v>11</v>
@@ -7480,21 +7474,21 @@
         <v>12</v>
       </c>
       <c r="G234" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="235" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C235" t="s">
         <v>308</v>
       </c>
       <c r="D235" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E235" t="s">
         <v>11</v>
@@ -7503,21 +7497,21 @@
         <v>12</v>
       </c>
       <c r="G235" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="236" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C236" t="s">
         <v>309</v>
       </c>
       <c r="D236" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E236" t="s">
         <v>11</v>
@@ -7526,21 +7520,21 @@
         <v>12</v>
       </c>
       <c r="G236" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="237" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B237" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C237" t="s">
         <v>310</v>
       </c>
       <c r="D237" t="s">
-        <v>130</v>
+        <v>311</v>
       </c>
       <c r="E237" t="s">
         <v>11</v>
@@ -7549,21 +7543,21 @@
         <v>12</v>
       </c>
       <c r="G237" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="238" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B238" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C238" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D238" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E238" t="s">
         <v>11</v>
@@ -7572,21 +7566,21 @@
         <v>12</v>
       </c>
       <c r="G238" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="239" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B239" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C239" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D239" t="s">
-        <v>314</v>
+        <v>146</v>
       </c>
       <c r="E239" t="s">
         <v>11</v>
@@ -7595,21 +7589,21 @@
         <v>12</v>
       </c>
       <c r="G239" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="240" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B240" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C240" t="s">
         <v>315</v>
       </c>
       <c r="D240" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E240" t="s">
         <v>11</v>
@@ -7618,21 +7612,21 @@
         <v>12</v>
       </c>
       <c r="G240" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="241" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B241" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C241" t="s">
         <v>316</v>
       </c>
       <c r="D241" t="s">
-        <v>148</v>
+        <v>317</v>
       </c>
       <c r="E241" t="s">
         <v>11</v>
@@ -7641,21 +7635,21 @@
         <v>12</v>
       </c>
       <c r="G241" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="242" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B242" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C242" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D242" t="s">
-        <v>318</v>
+        <v>158</v>
       </c>
       <c r="E242" t="s">
         <v>11</v>
@@ -7664,21 +7658,21 @@
         <v>12</v>
       </c>
       <c r="G242" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="243" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B243" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C243" t="s">
         <v>319</v>
       </c>
       <c r="D243" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E243" t="s">
         <v>11</v>
@@ -7687,21 +7681,21 @@
         <v>12</v>
       </c>
       <c r="G243" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="244" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B244" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C244" t="s">
         <v>320</v>
       </c>
       <c r="D244" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E244" t="s">
         <v>11</v>
@@ -7710,21 +7704,21 @@
         <v>12</v>
       </c>
       <c r="G244" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="245" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B245" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C245" t="s">
         <v>321</v>
       </c>
       <c r="D245" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="E245" t="s">
         <v>11</v>
@@ -7733,44 +7727,44 @@
         <v>12</v>
       </c>
       <c r="G245" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
     </row>
     <row r="246" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B246" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C246" t="s">
+        <v>323</v>
+      </c>
+      <c r="D246" t="s">
+        <v>106</v>
+      </c>
+      <c r="E246" t="s">
+        <v>11</v>
+      </c>
+      <c r="F246" t="s">
+        <v>12</v>
+      </c>
+      <c r="G246" t="s">
         <v>322</v>
-      </c>
-      <c r="D246" t="s">
-        <v>103</v>
-      </c>
-      <c r="E246" t="s">
-        <v>11</v>
-      </c>
-      <c r="F246" t="s">
-        <v>12</v>
-      </c>
-      <c r="G246" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="247" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B247" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C247" t="s">
         <v>324</v>
       </c>
       <c r="D247" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E247" t="s">
         <v>11</v>
@@ -7779,21 +7773,21 @@
         <v>12</v>
       </c>
       <c r="G247" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="248" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B248" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C248" t="s">
         <v>325</v>
       </c>
       <c r="D248" t="s">
-        <v>112</v>
+        <v>326</v>
       </c>
       <c r="E248" t="s">
         <v>11</v>
@@ -7802,21 +7796,21 @@
         <v>12</v>
       </c>
       <c r="G248" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="249" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B249" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C249" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D249" t="s">
-        <v>327</v>
+        <v>114</v>
       </c>
       <c r="E249" t="s">
         <v>11</v>
@@ -7825,21 +7819,21 @@
         <v>12</v>
       </c>
       <c r="G249" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="250" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B250" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C250" t="s">
         <v>328</v>
       </c>
       <c r="D250" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E250" t="s">
         <v>11</v>
@@ -7848,21 +7842,21 @@
         <v>12</v>
       </c>
       <c r="G250" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="251" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B251" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C251" t="s">
         <v>329</v>
       </c>
       <c r="D251" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E251" t="s">
         <v>11</v>
@@ -7871,21 +7865,21 @@
         <v>12</v>
       </c>
       <c r="G251" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="252" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B252" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C252" t="s">
         <v>330</v>
       </c>
       <c r="D252" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E252" t="s">
         <v>11</v>
@@ -7894,21 +7888,21 @@
         <v>12</v>
       </c>
       <c r="G252" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="253" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B253" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C253" t="s">
         <v>331</v>
       </c>
       <c r="D253" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E253" t="s">
         <v>11</v>
@@ -7917,21 +7911,21 @@
         <v>12</v>
       </c>
       <c r="G253" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="254" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B254" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C254" t="s">
         <v>332</v>
       </c>
       <c r="D254" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E254" t="s">
         <v>11</v>
@@ -7940,21 +7934,21 @@
         <v>12</v>
       </c>
       <c r="G254" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="255" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B255" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C255" t="s">
         <v>333</v>
       </c>
       <c r="D255" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E255" t="s">
         <v>11</v>
@@ -7963,21 +7957,21 @@
         <v>12</v>
       </c>
       <c r="G255" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="256" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B256" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C256" t="s">
         <v>334</v>
       </c>
       <c r="D256" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E256" t="s">
         <v>11</v>
@@ -7986,21 +7980,21 @@
         <v>12</v>
       </c>
       <c r="G256" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="257" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B257" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C257" t="s">
         <v>335</v>
       </c>
       <c r="D257" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E257" t="s">
         <v>11</v>
@@ -8009,21 +8003,21 @@
         <v>12</v>
       </c>
       <c r="G257" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="258" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B258" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C258" t="s">
         <v>336</v>
       </c>
       <c r="D258" t="s">
-        <v>130</v>
+        <v>311</v>
       </c>
       <c r="E258" t="s">
         <v>11</v>
@@ -8032,21 +8026,21 @@
         <v>12</v>
       </c>
       <c r="G258" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="259" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B259" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C259" t="s">
         <v>337</v>
       </c>
       <c r="D259" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E259" t="s">
         <v>11</v>
@@ -8055,21 +8049,21 @@
         <v>12</v>
       </c>
       <c r="G259" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="260" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B260" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C260" t="s">
         <v>338</v>
       </c>
       <c r="D260" t="s">
-        <v>314</v>
+        <v>146</v>
       </c>
       <c r="E260" t="s">
         <v>11</v>
@@ -8078,21 +8072,21 @@
         <v>12</v>
       </c>
       <c r="G260" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="261" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B261" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C261" t="s">
         <v>339</v>
       </c>
       <c r="D261" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E261" t="s">
         <v>11</v>
@@ -8101,21 +8095,21 @@
         <v>12</v>
       </c>
       <c r="G261" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="262" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B262" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C262" t="s">
         <v>340</v>
       </c>
       <c r="D262" t="s">
-        <v>148</v>
+        <v>317</v>
       </c>
       <c r="E262" t="s">
         <v>11</v>
@@ -8124,21 +8118,21 @@
         <v>12</v>
       </c>
       <c r="G262" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="263" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B263" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C263" t="s">
         <v>341</v>
       </c>
       <c r="D263" t="s">
-        <v>318</v>
+        <v>158</v>
       </c>
       <c r="E263" t="s">
         <v>11</v>
@@ -8147,21 +8141,21 @@
         <v>12</v>
       </c>
       <c r="G263" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="264" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B264" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C264" t="s">
         <v>342</v>
       </c>
       <c r="D264" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E264" t="s">
         <v>11</v>
@@ -8170,21 +8164,21 @@
         <v>12</v>
       </c>
       <c r="G264" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="265" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B265" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C265" t="s">
         <v>343</v>
       </c>
       <c r="D265" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E265" t="s">
         <v>11</v>
@@ -8193,21 +8187,21 @@
         <v>12</v>
       </c>
       <c r="G265" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="266" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B266" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C266" t="s">
         <v>344</v>
       </c>
       <c r="D266" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="E266" t="s">
         <v>11</v>
@@ -8216,21 +8210,21 @@
         <v>12</v>
       </c>
       <c r="G266" t="s">
-        <v>323</v>
+        <v>104</v>
       </c>
     </row>
     <row r="267" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B267" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C267" t="s">
         <v>345</v>
       </c>
       <c r="D267" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E267" t="s">
         <v>11</v>
@@ -8244,16 +8238,16 @@
     </row>
     <row r="268" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B268" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C268" t="s">
         <v>346</v>
       </c>
       <c r="D268" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E268" t="s">
         <v>11</v>
@@ -8267,16 +8261,16 @@
     </row>
     <row r="269" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B269" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C269" t="s">
         <v>347</v>
       </c>
       <c r="D269" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E269" t="s">
         <v>11</v>
@@ -8290,16 +8284,16 @@
     </row>
     <row r="270" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B270" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C270" t="s">
         <v>348</v>
       </c>
       <c r="D270" t="s">
-        <v>112</v>
+        <v>326</v>
       </c>
       <c r="E270" t="s">
         <v>11</v>
@@ -8313,16 +8307,16 @@
     </row>
     <row r="271" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B271" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C271" t="s">
         <v>349</v>
       </c>
       <c r="D271" t="s">
-        <v>327</v>
+        <v>114</v>
       </c>
       <c r="E271" t="s">
         <v>11</v>
@@ -8336,16 +8330,16 @@
     </row>
     <row r="272" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B272" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C272" t="s">
         <v>350</v>
       </c>
       <c r="D272" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E272" t="s">
         <v>11</v>
@@ -8359,16 +8353,16 @@
     </row>
     <row r="273" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B273" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C273" t="s">
         <v>351</v>
       </c>
       <c r="D273" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E273" t="s">
         <v>11</v>
@@ -8382,16 +8376,16 @@
     </row>
     <row r="274" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B274" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C274" t="s">
         <v>352</v>
       </c>
       <c r="D274" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E274" t="s">
         <v>11</v>
@@ -8405,16 +8399,16 @@
     </row>
     <row r="275" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B275" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C275" t="s">
         <v>353</v>
       </c>
       <c r="D275" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E275" t="s">
         <v>11</v>
@@ -8428,16 +8422,16 @@
     </row>
     <row r="276" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B276" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C276" t="s">
         <v>354</v>
       </c>
       <c r="D276" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E276" t="s">
         <v>11</v>
@@ -8451,16 +8445,16 @@
     </row>
     <row r="277" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B277" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C277" t="s">
         <v>355</v>
       </c>
       <c r="D277" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E277" t="s">
         <v>11</v>
@@ -8474,16 +8468,16 @@
     </row>
     <row r="278" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B278" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C278" t="s">
         <v>356</v>
       </c>
       <c r="D278" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E278" t="s">
         <v>11</v>
@@ -8497,16 +8491,16 @@
     </row>
     <row r="279" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B279" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C279" t="s">
         <v>357</v>
       </c>
       <c r="D279" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E279" t="s">
         <v>11</v>
@@ -8520,16 +8514,16 @@
     </row>
     <row r="280" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B280" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C280" t="s">
         <v>358</v>
       </c>
       <c r="D280" t="s">
-        <v>130</v>
+        <v>311</v>
       </c>
       <c r="E280" t="s">
         <v>11</v>
@@ -8543,16 +8537,16 @@
     </row>
     <row r="281" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B281" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C281" t="s">
         <v>359</v>
       </c>
       <c r="D281" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E281" t="s">
         <v>11</v>
@@ -8566,16 +8560,16 @@
     </row>
     <row r="282" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B282" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C282" t="s">
         <v>360</v>
       </c>
       <c r="D282" t="s">
-        <v>314</v>
+        <v>132</v>
       </c>
       <c r="E282" t="s">
         <v>11</v>
@@ -8589,16 +8583,16 @@
     </row>
     <row r="283" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B283" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C283" t="s">
         <v>361</v>
       </c>
       <c r="D283" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E283" t="s">
         <v>11</v>
@@ -8612,16 +8606,16 @@
     </row>
     <row r="284" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B284" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C284" t="s">
         <v>362</v>
       </c>
       <c r="D284" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E284" t="s">
         <v>11</v>
@@ -8635,16 +8629,16 @@
     </row>
     <row r="285" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B285" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C285" t="s">
         <v>363</v>
       </c>
       <c r="D285" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E285" t="s">
         <v>11</v>
@@ -8658,16 +8652,16 @@
     </row>
     <row r="286" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B286" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C286" t="s">
         <v>364</v>
       </c>
       <c r="D286" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E286" t="s">
         <v>11</v>
@@ -8681,16 +8675,16 @@
     </row>
     <row r="287" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B287" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C287" t="s">
         <v>365</v>
       </c>
       <c r="D287" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E287" t="s">
         <v>11</v>
@@ -8704,16 +8698,16 @@
     </row>
     <row r="288" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B288" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C288" t="s">
         <v>366</v>
       </c>
       <c r="D288" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E288" t="s">
         <v>11</v>
@@ -8727,16 +8721,16 @@
     </row>
     <row r="289" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B289" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C289" t="s">
         <v>367</v>
       </c>
       <c r="D289" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E289" t="s">
         <v>11</v>
@@ -8750,16 +8744,16 @@
     </row>
     <row r="290" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B290" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C290" t="s">
         <v>368</v>
       </c>
       <c r="D290" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E290" t="s">
         <v>11</v>
@@ -8773,16 +8767,16 @@
     </row>
     <row r="291" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B291" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C291" t="s">
         <v>369</v>
       </c>
       <c r="D291" t="s">
-        <v>148</v>
+        <v>317</v>
       </c>
       <c r="E291" t="s">
         <v>11</v>
@@ -8796,16 +8790,16 @@
     </row>
     <row r="292" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B292" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C292" t="s">
         <v>370</v>
       </c>
       <c r="D292" t="s">
-        <v>318</v>
+        <v>158</v>
       </c>
       <c r="E292" t="s">
         <v>11</v>
@@ -8819,16 +8813,16 @@
     </row>
     <row r="293" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B293" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C293" t="s">
         <v>371</v>
       </c>
       <c r="D293" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E293" t="s">
         <v>11</v>
@@ -8842,16 +8836,16 @@
     </row>
     <row r="294" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B294" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C294" t="s">
         <v>372</v>
       </c>
       <c r="D294" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E294" t="s">
         <v>11</v>
@@ -8865,16 +8859,16 @@
     </row>
     <row r="295" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B295" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C295" t="s">
         <v>373</v>
       </c>
       <c r="D295" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="E295" t="s">
         <v>11</v>
@@ -8883,21 +8877,21 @@
         <v>12</v>
       </c>
       <c r="G295" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
     </row>
     <row r="296" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B296" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C296" t="s">
         <v>374</v>
       </c>
       <c r="D296" t="s">
-        <v>108</v>
+        <v>326</v>
       </c>
       <c r="E296" t="s">
         <v>11</v>
@@ -8911,16 +8905,16 @@
     </row>
     <row r="297" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B297" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C297" t="s">
         <v>375</v>
       </c>
       <c r="D297" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E297" t="s">
         <v>11</v>
@@ -8934,16 +8928,16 @@
     </row>
     <row r="298" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B298" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C298" t="s">
         <v>376</v>
       </c>
       <c r="D298" t="s">
-        <v>327</v>
+        <v>116</v>
       </c>
       <c r="E298" t="s">
         <v>11</v>
@@ -8957,16 +8951,16 @@
     </row>
     <row r="299" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B299" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C299" t="s">
         <v>377</v>
       </c>
       <c r="D299" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E299" t="s">
         <v>11</v>
@@ -8980,16 +8974,16 @@
     </row>
     <row r="300" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B300" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C300" t="s">
         <v>378</v>
       </c>
       <c r="D300" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E300" t="s">
         <v>11</v>
@@ -9003,16 +8997,16 @@
     </row>
     <row r="301" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B301" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C301" t="s">
         <v>379</v>
       </c>
       <c r="D301" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E301" t="s">
         <v>11</v>
@@ -9026,16 +9020,16 @@
     </row>
     <row r="302" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B302" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C302" t="s">
         <v>380</v>
       </c>
       <c r="D302" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E302" t="s">
         <v>11</v>
@@ -9049,16 +9043,16 @@
     </row>
     <row r="303" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B303" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C303" t="s">
         <v>381</v>
       </c>
       <c r="D303" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E303" t="s">
         <v>11</v>
@@ -9072,16 +9066,16 @@
     </row>
     <row r="304" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B304" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C304" t="s">
         <v>382</v>
       </c>
       <c r="D304" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E304" t="s">
         <v>11</v>
@@ -9095,16 +9089,16 @@
     </row>
     <row r="305" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B305" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C305" t="s">
         <v>383</v>
       </c>
       <c r="D305" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E305" t="s">
         <v>11</v>
@@ -9118,16 +9112,16 @@
     </row>
     <row r="306" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B306" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C306" t="s">
         <v>384</v>
       </c>
       <c r="D306" t="s">
-        <v>128</v>
+        <v>311</v>
       </c>
       <c r="E306" t="s">
         <v>11</v>
@@ -9141,16 +9135,16 @@
     </row>
     <row r="307" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B307" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C307" t="s">
         <v>385</v>
       </c>
       <c r="D307" t="s">
-        <v>130</v>
+        <v>313</v>
       </c>
       <c r="E307" t="s">
         <v>11</v>
@@ -9164,16 +9158,16 @@
     </row>
     <row r="308" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B308" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C308" t="s">
         <v>386</v>
       </c>
       <c r="D308" t="s">
-        <v>312</v>
+        <v>132</v>
       </c>
       <c r="E308" t="s">
         <v>11</v>
@@ -9187,16 +9181,16 @@
     </row>
     <row r="309" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B309" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C309" t="s">
         <v>387</v>
       </c>
       <c r="D309" t="s">
-        <v>314</v>
+        <v>134</v>
       </c>
       <c r="E309" t="s">
         <v>11</v>
@@ -9210,16 +9204,16 @@
     </row>
     <row r="310" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B310" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C310" t="s">
         <v>388</v>
       </c>
       <c r="D310" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E310" t="s">
         <v>11</v>
@@ -9233,16 +9227,16 @@
     </row>
     <row r="311" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B311" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C311" t="s">
         <v>389</v>
       </c>
       <c r="D311" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E311" t="s">
         <v>11</v>
@@ -9256,16 +9250,16 @@
     </row>
     <row r="312" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B312" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C312" t="s">
         <v>390</v>
       </c>
       <c r="D312" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E312" t="s">
         <v>11</v>
@@ -9279,16 +9273,16 @@
     </row>
     <row r="313" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B313" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C313" t="s">
         <v>391</v>
       </c>
       <c r="D313" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E313" t="s">
         <v>11</v>
@@ -9302,16 +9296,16 @@
     </row>
     <row r="314" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B314" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C314" t="s">
         <v>392</v>
       </c>
       <c r="D314" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E314" t="s">
         <v>11</v>
@@ -9325,16 +9319,16 @@
     </row>
     <row r="315" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B315" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C315" t="s">
         <v>393</v>
       </c>
       <c r="D315" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E315" t="s">
         <v>11</v>
@@ -9348,16 +9342,16 @@
     </row>
     <row r="316" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B316" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C316" t="s">
         <v>394</v>
       </c>
       <c r="D316" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E316" t="s">
         <v>11</v>
@@ -9371,16 +9365,16 @@
     </row>
     <row r="317" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B317" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C317" t="s">
         <v>395</v>
       </c>
       <c r="D317" t="s">
-        <v>146</v>
+        <v>317</v>
       </c>
       <c r="E317" t="s">
         <v>11</v>
@@ -9394,16 +9388,16 @@
     </row>
     <row r="318" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B318" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C318" t="s">
         <v>396</v>
       </c>
       <c r="D318" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E318" t="s">
         <v>11</v>
@@ -9417,16 +9411,16 @@
     </row>
     <row r="319" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B319" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C319" t="s">
         <v>397</v>
       </c>
       <c r="D319" t="s">
-        <v>318</v>
+        <v>160</v>
       </c>
       <c r="E319" t="s">
         <v>11</v>
@@ -9440,16 +9434,16 @@
     </row>
     <row r="320" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B320" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C320" t="s">
         <v>398</v>
       </c>
       <c r="D320" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E320" t="s">
         <v>11</v>
@@ -9463,548 +9457,548 @@
     </row>
     <row r="321" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>235</v>
+        <v>399</v>
       </c>
       <c r="B321" t="s">
-        <v>236</v>
+        <v>400</v>
       </c>
       <c r="C321" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D321" t="s">
-        <v>160</v>
+        <v>402</v>
       </c>
       <c r="E321" t="s">
-        <v>11</v>
+        <v>403</v>
       </c>
       <c r="F321" t="s">
         <v>12</v>
       </c>
       <c r="G321" t="s">
-        <v>166</v>
+        <v>237</v>
       </c>
     </row>
     <row r="322" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>235</v>
+        <v>399</v>
       </c>
       <c r="B322" t="s">
-        <v>236</v>
+        <v>400</v>
       </c>
       <c r="C322" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D322" t="s">
-        <v>162</v>
+        <v>402</v>
       </c>
       <c r="E322" t="s">
-        <v>11</v>
+        <v>403</v>
       </c>
       <c r="F322" t="s">
         <v>12</v>
       </c>
       <c r="G322" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
     </row>
     <row r="323" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B323" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C323" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D323" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E323" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F323" t="s">
         <v>12</v>
       </c>
       <c r="G323" t="s">
-        <v>238</v>
+        <v>277</v>
       </c>
     </row>
     <row r="324" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B324" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C324" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D324" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E324" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F324" t="s">
         <v>12</v>
       </c>
       <c r="G324" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
     </row>
     <row r="325" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B325" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C325" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D325" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E325" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F325" t="s">
         <v>12</v>
       </c>
       <c r="G325" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="326" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B326" t="s">
+        <v>400</v>
+      </c>
+      <c r="C326" t="s">
+        <v>411</v>
+      </c>
+      <c r="D326" t="s">
         <v>402</v>
       </c>
-      <c r="C326" t="s">
-        <v>409</v>
-      </c>
-      <c r="D326" t="s">
-        <v>410</v>
-      </c>
       <c r="E326" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F326" t="s">
         <v>12</v>
       </c>
       <c r="G326" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="327" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B327" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C327" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D327" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E327" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F327" t="s">
         <v>12</v>
       </c>
       <c r="G327" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="328" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B328" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C328" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D328" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E328" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F328" t="s">
         <v>12</v>
       </c>
       <c r="G328" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
     </row>
     <row r="329" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B329" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C329" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D329" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="E329" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F329" t="s">
         <v>12</v>
       </c>
       <c r="G329" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
     </row>
     <row r="330" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B330" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C330" t="s">
         <v>416</v>
       </c>
       <c r="D330" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E330" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F330" t="s">
         <v>12</v>
       </c>
       <c r="G330" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="331" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B331" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C331" t="s">
         <v>417</v>
       </c>
       <c r="D331" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E331" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F331" t="s">
         <v>12</v>
       </c>
       <c r="G331" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="332" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B332" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C332" t="s">
         <v>418</v>
       </c>
       <c r="D332" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E332" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F332" t="s">
         <v>12</v>
       </c>
       <c r="G332" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
     </row>
     <row r="333" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B333" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C333" t="s">
         <v>419</v>
       </c>
       <c r="D333" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E333" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F333" t="s">
         <v>12</v>
       </c>
       <c r="G333" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
     </row>
     <row r="334" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B334" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C334" t="s">
         <v>420</v>
       </c>
       <c r="D334" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E334" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F334" t="s">
         <v>12</v>
       </c>
       <c r="G334" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="335" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B335" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C335" t="s">
         <v>421</v>
       </c>
       <c r="D335" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E335" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F335" t="s">
         <v>12</v>
       </c>
       <c r="G335" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="336" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B336" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C336" t="s">
         <v>422</v>
       </c>
       <c r="D336" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="E336" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F336" t="s">
         <v>12</v>
       </c>
       <c r="G336" t="s">
-        <v>323</v>
+        <v>166</v>
       </c>
     </row>
     <row r="337" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B337" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C337" t="s">
+        <v>424</v>
+      </c>
+      <c r="D337" t="s">
         <v>423</v>
       </c>
-      <c r="D337" t="s">
-        <v>404</v>
-      </c>
       <c r="E337" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F337" t="s">
         <v>12</v>
       </c>
       <c r="G337" t="s">
-        <v>323</v>
+        <v>196</v>
       </c>
     </row>
     <row r="338" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B338" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C338" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D338" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E338" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F338" t="s">
         <v>12</v>
       </c>
       <c r="G338" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
     </row>
     <row r="339" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B339" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C339" t="s">
         <v>426</v>
       </c>
       <c r="D339" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E339" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F339" t="s">
         <v>12</v>
       </c>
       <c r="G339" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
     </row>
     <row r="340" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B340" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C340" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D340" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E340" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F340" t="s">
         <v>12</v>
       </c>
       <c r="G340" t="s">
-        <v>209</v>
+        <v>41</v>
       </c>
     </row>
     <row r="341" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B341" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C341" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D341" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E341" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F341" t="s">
         <v>12</v>
       </c>
       <c r="G341" t="s">
-        <v>166</v>
+        <v>41</v>
       </c>
     </row>
     <row r="342" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B342" t="s">
+        <v>400</v>
+      </c>
+      <c r="C342" t="s">
+        <v>432</v>
+      </c>
+      <c r="D342" t="s">
         <v>402</v>
       </c>
-      <c r="C342" t="s">
-        <v>430</v>
-      </c>
-      <c r="D342" t="s">
-        <v>431</v>
-      </c>
       <c r="E342" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F342" t="s">
         <v>12</v>
       </c>
       <c r="G342" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
     </row>
     <row r="343" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B343" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C343" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D343" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E343" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F343" t="s">
         <v>12</v>
       </c>
       <c r="G343" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
     </row>
     <row r="344" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B344" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C344" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D344" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E344" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F344" t="s">
         <v>12</v>
@@ -10015,19 +10009,19 @@
     </row>
     <row r="345" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B345" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C345" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D345" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E345" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F345" t="s">
         <v>12</v>
@@ -10038,19 +10032,19 @@
     </row>
     <row r="346" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B346" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C346" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D346" t="s">
         <v>410</v>
       </c>
       <c r="E346" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F346" t="s">
         <v>12</v>
@@ -10061,240 +10055,240 @@
     </row>
     <row r="347" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B347" t="s">
+        <v>400</v>
+      </c>
+      <c r="C347" t="s">
+        <v>439</v>
+      </c>
+      <c r="D347" t="s">
         <v>402</v>
       </c>
-      <c r="C347" t="s">
-        <v>438</v>
-      </c>
-      <c r="D347" t="s">
-        <v>439</v>
-      </c>
       <c r="E347" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F347" t="s">
         <v>12</v>
       </c>
       <c r="G347" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
     </row>
     <row r="348" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B348" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C348" t="s">
         <v>440</v>
       </c>
       <c r="D348" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="E348" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F348" t="s">
         <v>12</v>
       </c>
       <c r="G348" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
     </row>
     <row r="349" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B349" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C349" t="s">
         <v>441</v>
       </c>
       <c r="D349" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E349" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F349" t="s">
         <v>12</v>
       </c>
       <c r="G349" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="350" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B350" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C350" t="s">
         <v>442</v>
       </c>
       <c r="D350" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E350" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F350" t="s">
         <v>12</v>
       </c>
       <c r="G350" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="351" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B351" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C351" t="s">
         <v>443</v>
       </c>
       <c r="D351" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="E351" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F351" t="s">
         <v>12</v>
       </c>
       <c r="G351" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="352" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B352" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C352" t="s">
         <v>444</v>
       </c>
       <c r="D352" t="s">
-        <v>439</v>
+        <v>410</v>
       </c>
       <c r="E352" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F352" t="s">
         <v>12</v>
       </c>
       <c r="G352" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="353" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B353" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C353" t="s">
         <v>445</v>
       </c>
       <c r="D353" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="E353" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F353" t="s">
         <v>12</v>
       </c>
       <c r="G353" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="354" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B354" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C354" t="s">
         <v>446</v>
       </c>
       <c r="D354" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="E354" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F354" t="s">
         <v>12</v>
       </c>
       <c r="G354" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="355" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B355" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C355" t="s">
         <v>447</v>
       </c>
       <c r="D355" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E355" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F355" t="s">
         <v>12</v>
       </c>
       <c r="G355" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="356" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B356" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C356" t="s">
         <v>448</v>
       </c>
       <c r="D356" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E356" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F356" t="s">
         <v>12</v>
       </c>
       <c r="G356" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="357" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B357" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C357" t="s">
         <v>449</v>
@@ -10303,113 +10297,113 @@
         <v>410</v>
       </c>
       <c r="E357" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F357" t="s">
         <v>12</v>
       </c>
       <c r="G357" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="358" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B358" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C358" t="s">
         <v>450</v>
       </c>
       <c r="D358" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="E358" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F358" t="s">
         <v>12</v>
       </c>
       <c r="G358" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
     </row>
     <row r="359" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B359" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C359" t="s">
         <v>451</v>
       </c>
       <c r="D359" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="E359" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F359" t="s">
         <v>12</v>
       </c>
       <c r="G359" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
     </row>
     <row r="360" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B360" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C360" t="s">
         <v>452</v>
       </c>
       <c r="D360" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E360" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F360" t="s">
         <v>12</v>
       </c>
       <c r="G360" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="361" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B361" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C361" t="s">
         <v>453</v>
       </c>
       <c r="D361" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E361" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F361" t="s">
         <v>12</v>
       </c>
       <c r="G361" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="362" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B362" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C362" t="s">
         <v>454</v>
@@ -10418,76 +10412,76 @@
         <v>410</v>
       </c>
       <c r="E362" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F362" t="s">
         <v>12</v>
       </c>
       <c r="G362" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="363" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B363" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C363" t="s">
         <v>455</v>
       </c>
       <c r="D363" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="E363" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F363" t="s">
         <v>12</v>
       </c>
       <c r="G363" t="s">
-        <v>221</v>
+        <v>13</v>
       </c>
     </row>
     <row r="364" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B364" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C364" t="s">
         <v>456</v>
       </c>
       <c r="D364" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="E364" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F364" t="s">
         <v>12</v>
       </c>
       <c r="G364" t="s">
-        <v>221</v>
+        <v>13</v>
       </c>
     </row>
     <row r="365" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B365" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C365" t="s">
         <v>457</v>
       </c>
       <c r="D365" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E365" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F365" t="s">
         <v>12</v>
@@ -10498,19 +10492,19 @@
     </row>
     <row r="366" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B366" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C366" t="s">
         <v>458</v>
       </c>
       <c r="D366" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E366" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F366" t="s">
         <v>12</v>
@@ -10521,10 +10515,10 @@
     </row>
     <row r="367" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B367" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C367" t="s">
         <v>459</v>
@@ -10533,7 +10527,7 @@
         <v>410</v>
       </c>
       <c r="E367" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F367" t="s">
         <v>12</v>
@@ -10544,65 +10538,65 @@
     </row>
     <row r="368" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B368" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C368" t="s">
         <v>460</v>
       </c>
       <c r="D368" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="E368" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F368" t="s">
         <v>12</v>
       </c>
       <c r="G368" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="369" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B369" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C369" t="s">
         <v>461</v>
       </c>
       <c r="D369" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="E369" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F369" t="s">
         <v>12</v>
       </c>
       <c r="G369" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="370" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B370" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C370" t="s">
         <v>462</v>
       </c>
       <c r="D370" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E370" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F370" t="s">
         <v>12</v>
@@ -10613,19 +10607,19 @@
     </row>
     <row r="371" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B371" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C371" t="s">
         <v>463</v>
       </c>
       <c r="D371" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="E371" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F371" t="s">
         <v>12</v>
@@ -10636,594 +10630,594 @@
     </row>
     <row r="372" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B372" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C372" t="s">
         <v>464</v>
       </c>
       <c r="D372" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="E372" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F372" t="s">
         <v>12</v>
       </c>
       <c r="G372" t="s">
-        <v>41</v>
+        <v>196</v>
       </c>
     </row>
     <row r="373" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B373" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C373" t="s">
         <v>465</v>
       </c>
       <c r="D373" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="E373" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F373" t="s">
         <v>12</v>
       </c>
       <c r="G373" t="s">
-        <v>41</v>
+        <v>208</v>
       </c>
     </row>
     <row r="374" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B374" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C374" t="s">
         <v>466</v>
       </c>
       <c r="D374" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="E374" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F374" t="s">
         <v>12</v>
       </c>
       <c r="G374" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="375" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>401</v>
+        <v>467</v>
       </c>
       <c r="B375" t="s">
-        <v>402</v>
+        <v>468</v>
       </c>
       <c r="C375" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D375" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="E375" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F375" t="s">
         <v>12</v>
       </c>
       <c r="G375" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
     </row>
     <row r="376" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>401</v>
+        <v>467</v>
       </c>
       <c r="B376" t="s">
-        <v>402</v>
+        <v>468</v>
       </c>
       <c r="C376" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D376" t="s">
         <v>408</v>
       </c>
       <c r="E376" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F376" t="s">
         <v>12</v>
       </c>
       <c r="G376" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
     </row>
     <row r="377" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B377" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C377" t="s">
         <v>471</v>
       </c>
       <c r="D377" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E377" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F377" t="s">
         <v>12</v>
       </c>
       <c r="G377" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="378" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B378" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C378" t="s">
         <v>472</v>
       </c>
       <c r="D378" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E378" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F378" t="s">
         <v>12</v>
       </c>
       <c r="G378" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
     </row>
     <row r="379" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B379" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C379" t="s">
         <v>473</v>
       </c>
       <c r="D379" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E379" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F379" t="s">
         <v>12</v>
       </c>
       <c r="G379" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
     </row>
     <row r="380" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B380" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C380" t="s">
         <v>474</v>
       </c>
       <c r="D380" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E380" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F380" t="s">
         <v>12</v>
       </c>
       <c r="G380" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="381" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B381" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C381" t="s">
         <v>475</v>
       </c>
       <c r="D381" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E381" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F381" t="s">
         <v>12</v>
       </c>
       <c r="G381" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
     </row>
     <row r="382" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B382" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C382" t="s">
         <v>476</v>
       </c>
       <c r="D382" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E382" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F382" t="s">
         <v>12</v>
       </c>
       <c r="G382" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
     </row>
     <row r="383" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B383" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C383" t="s">
         <v>477</v>
       </c>
       <c r="D383" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E383" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F383" t="s">
         <v>12</v>
       </c>
       <c r="G383" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="384" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B384" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C384" t="s">
         <v>478</v>
       </c>
       <c r="D384" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E384" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F384" t="s">
         <v>12</v>
       </c>
       <c r="G384" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
     </row>
     <row r="385" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B385" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C385" t="s">
         <v>479</v>
       </c>
       <c r="D385" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E385" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F385" t="s">
         <v>12</v>
       </c>
       <c r="G385" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
     </row>
     <row r="386" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B386" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C386" t="s">
         <v>480</v>
       </c>
       <c r="D386" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E386" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F386" t="s">
         <v>12</v>
       </c>
       <c r="G386" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="387" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B387" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C387" t="s">
         <v>481</v>
       </c>
       <c r="D387" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E387" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F387" t="s">
         <v>12</v>
       </c>
       <c r="G387" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
     </row>
     <row r="388" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B388" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C388" t="s">
         <v>482</v>
       </c>
       <c r="D388" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E388" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F388" t="s">
         <v>12</v>
       </c>
       <c r="G388" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
     </row>
     <row r="389" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B389" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C389" t="s">
         <v>483</v>
       </c>
       <c r="D389" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E389" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F389" t="s">
         <v>12</v>
       </c>
       <c r="G389" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="390" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B390" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C390" t="s">
         <v>484</v>
       </c>
       <c r="D390" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E390" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F390" t="s">
         <v>12</v>
       </c>
       <c r="G390" t="s">
-        <v>323</v>
+        <v>237</v>
       </c>
     </row>
     <row r="391" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B391" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C391" t="s">
         <v>485</v>
       </c>
       <c r="D391" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="E391" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F391" t="s">
         <v>12</v>
       </c>
       <c r="G391" t="s">
-        <v>323</v>
+        <v>257</v>
       </c>
     </row>
     <row r="392" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B392" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C392" t="s">
         <v>486</v>
       </c>
       <c r="D392" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E392" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F392" t="s">
         <v>12</v>
       </c>
       <c r="G392" t="s">
-        <v>238</v>
+        <v>277</v>
       </c>
     </row>
     <row r="393" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B393" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C393" t="s">
         <v>487</v>
       </c>
       <c r="D393" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E393" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F393" t="s">
         <v>12</v>
       </c>
       <c r="G393" t="s">
-        <v>258</v>
+        <v>296</v>
       </c>
     </row>
     <row r="394" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B394" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C394" t="s">
         <v>488</v>
       </c>
       <c r="D394" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E394" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F394" t="s">
         <v>12</v>
       </c>
       <c r="G394" t="s">
-        <v>278</v>
+        <v>322</v>
       </c>
     </row>
     <row r="395" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B395" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C395" t="s">
         <v>489</v>
       </c>
       <c r="D395" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E395" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F395" t="s">
         <v>12</v>
       </c>
       <c r="G395" t="s">
-        <v>297</v>
+        <v>166</v>
       </c>
     </row>
     <row r="396" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B396" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C396" t="s">
         <v>490</v>
       </c>
       <c r="D396" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E396" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F396" t="s">
         <v>12</v>
       </c>
       <c r="G396" t="s">
-        <v>323</v>
+        <v>166</v>
       </c>
     </row>
     <row r="397" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B397" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C397" t="s">
         <v>491</v>
       </c>
       <c r="D397" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E397" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F397" t="s">
         <v>12</v>
@@ -11234,318 +11228,318 @@
     </row>
     <row r="398" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B398" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C398" t="s">
         <v>492</v>
       </c>
       <c r="D398" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E398" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F398" t="s">
         <v>12</v>
       </c>
       <c r="G398" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
     </row>
     <row r="399" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B399" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C399" t="s">
         <v>493</v>
       </c>
       <c r="D399" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E399" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F399" t="s">
         <v>12</v>
       </c>
       <c r="G399" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
     </row>
     <row r="400" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B400" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C400" t="s">
         <v>494</v>
       </c>
       <c r="D400" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E400" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F400" t="s">
         <v>12</v>
       </c>
       <c r="G400" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="401" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B401" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C401" t="s">
         <v>495</v>
       </c>
       <c r="D401" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E401" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F401" t="s">
         <v>12</v>
       </c>
       <c r="G401" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="402" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B402" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C402" t="s">
         <v>496</v>
       </c>
       <c r="D402" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E402" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F402" t="s">
         <v>12</v>
       </c>
       <c r="G402" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="403" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B403" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C403" t="s">
         <v>497</v>
       </c>
       <c r="D403" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E403" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F403" t="s">
         <v>12</v>
       </c>
       <c r="G403" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="404" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B404" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C404" t="s">
         <v>498</v>
       </c>
       <c r="D404" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E404" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F404" t="s">
         <v>12</v>
       </c>
       <c r="G404" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="405" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B405" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C405" t="s">
         <v>499</v>
       </c>
       <c r="D405" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E405" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F405" t="s">
         <v>12</v>
       </c>
       <c r="G405" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
     </row>
     <row r="406" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B406" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C406" t="s">
         <v>500</v>
       </c>
       <c r="D406" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E406" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F406" t="s">
         <v>12</v>
       </c>
       <c r="G406" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
     </row>
     <row r="407" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B407" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C407" t="s">
         <v>501</v>
       </c>
       <c r="D407" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E407" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F407" t="s">
         <v>12</v>
       </c>
       <c r="G407" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="408" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B408" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C408" t="s">
         <v>502</v>
       </c>
       <c r="D408" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E408" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F408" t="s">
         <v>12</v>
       </c>
       <c r="G408" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="409" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B409" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C409" t="s">
         <v>503</v>
       </c>
       <c r="D409" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E409" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F409" t="s">
         <v>12</v>
       </c>
       <c r="G409" t="s">
-        <v>221</v>
+        <v>13</v>
       </c>
     </row>
     <row r="410" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B410" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C410" t="s">
         <v>504</v>
       </c>
       <c r="D410" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E410" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F410" t="s">
         <v>12</v>
       </c>
       <c r="G410" t="s">
-        <v>221</v>
+        <v>13</v>
       </c>
     </row>
     <row r="411" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B411" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C411" t="s">
         <v>505</v>
       </c>
       <c r="D411" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E411" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F411" t="s">
         <v>12</v>
@@ -11556,19 +11550,19 @@
     </row>
     <row r="412" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B412" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C412" t="s">
         <v>506</v>
       </c>
       <c r="D412" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E412" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F412" t="s">
         <v>12</v>
@@ -11579,65 +11573,65 @@
     </row>
     <row r="413" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B413" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C413" t="s">
         <v>507</v>
       </c>
       <c r="D413" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E413" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F413" t="s">
         <v>12</v>
       </c>
       <c r="G413" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="414" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B414" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C414" t="s">
         <v>508</v>
       </c>
       <c r="D414" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E414" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F414" t="s">
         <v>12</v>
       </c>
       <c r="G414" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="415" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B415" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C415" t="s">
         <v>509</v>
       </c>
       <c r="D415" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E415" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F415" t="s">
         <v>12</v>
@@ -11648,19 +11642,19 @@
     </row>
     <row r="416" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B416" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C416" t="s">
         <v>510</v>
       </c>
       <c r="D416" t="s">
-        <v>408</v>
+        <v>511</v>
       </c>
       <c r="E416" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F416" t="s">
         <v>12</v>
@@ -11671,19 +11665,19 @@
     </row>
     <row r="417" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B417" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C417" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D417" t="s">
         <v>410</v>
       </c>
       <c r="E417" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F417" t="s">
         <v>12</v>
@@ -11694,65 +11688,65 @@
     </row>
     <row r="418" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B418" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C418" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D418" t="s">
-        <v>513</v>
+        <v>402</v>
       </c>
       <c r="E418" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F418" t="s">
         <v>12</v>
       </c>
       <c r="G418" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="419" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B419" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C419" t="s">
         <v>514</v>
       </c>
       <c r="D419" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E419" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F419" t="s">
         <v>12</v>
       </c>
       <c r="G419" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="420" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B420" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C420" t="s">
         <v>515</v>
       </c>
       <c r="D420" t="s">
-        <v>404</v>
+        <v>511</v>
       </c>
       <c r="E420" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F420" t="s">
         <v>12</v>
@@ -11763,65 +11757,65 @@
     </row>
     <row r="421" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B421" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C421" t="s">
         <v>516</v>
       </c>
       <c r="D421" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="E421" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F421" t="s">
         <v>12</v>
       </c>
       <c r="G421" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
     </row>
     <row r="422" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B422" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C422" t="s">
         <v>517</v>
       </c>
       <c r="D422" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="E422" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F422" t="s">
         <v>12</v>
       </c>
       <c r="G422" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
     </row>
     <row r="423" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B423" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C423" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D423" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E423" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F423" t="s">
         <v>12</v>
@@ -11832,19 +11826,19 @@
     </row>
     <row r="424" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B424" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C424" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D424" t="s">
-        <v>520</v>
+        <v>408</v>
       </c>
       <c r="E424" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F424" t="s">
         <v>12</v>
@@ -11855,19 +11849,19 @@
     </row>
     <row r="425" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B425" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C425" t="s">
         <v>521</v>
       </c>
       <c r="D425" t="s">
-        <v>408</v>
+        <v>511</v>
       </c>
       <c r="E425" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F425" t="s">
         <v>12</v>
@@ -11878,10 +11872,10 @@
     </row>
     <row r="426" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B426" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C426" t="s">
         <v>522</v>
@@ -11890,7 +11884,7 @@
         <v>410</v>
       </c>
       <c r="E426" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F426" t="s">
         <v>12</v>
@@ -11901,824 +11895,824 @@
     </row>
     <row r="427" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>469</v>
+        <v>523</v>
       </c>
       <c r="B427" t="s">
-        <v>470</v>
+        <v>524</v>
       </c>
       <c r="C427" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D427" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="E427" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F427" t="s">
         <v>12</v>
       </c>
       <c r="G427" t="s">
-        <v>73</v>
+        <v>237</v>
       </c>
     </row>
     <row r="428" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>469</v>
+        <v>523</v>
       </c>
       <c r="B428" t="s">
-        <v>470</v>
+        <v>524</v>
       </c>
       <c r="C428" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D428" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="E428" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F428" t="s">
         <v>12</v>
       </c>
       <c r="G428" t="s">
-        <v>73</v>
+        <v>237</v>
       </c>
     </row>
     <row r="429" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B429" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C429" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D429" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E429" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F429" t="s">
         <v>12</v>
       </c>
       <c r="G429" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="430" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B430" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C430" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D430" t="s">
-        <v>404</v>
+        <v>531</v>
       </c>
       <c r="E430" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F430" t="s">
         <v>12</v>
       </c>
       <c r="G430" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="431" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B431" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C431" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D431" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E431" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F431" t="s">
         <v>12</v>
       </c>
       <c r="G431" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="432" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B432" t="s">
+        <v>524</v>
+      </c>
+      <c r="C432" t="s">
+        <v>534</v>
+      </c>
+      <c r="D432" t="s">
         <v>526</v>
       </c>
-      <c r="C432" t="s">
-        <v>532</v>
-      </c>
-      <c r="D432" t="s">
-        <v>533</v>
-      </c>
       <c r="E432" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F432" t="s">
         <v>12</v>
       </c>
       <c r="G432" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
     </row>
     <row r="433" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B433" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C433" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D433" t="s">
-        <v>535</v>
+        <v>402</v>
       </c>
       <c r="E433" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F433" t="s">
         <v>12</v>
       </c>
       <c r="G433" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
     </row>
     <row r="434" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B434" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C434" t="s">
         <v>536</v>
       </c>
       <c r="D434" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E434" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F434" t="s">
         <v>12</v>
       </c>
       <c r="G434" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="435" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B435" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C435" t="s">
         <v>537</v>
       </c>
       <c r="D435" t="s">
-        <v>404</v>
+        <v>531</v>
       </c>
       <c r="E435" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F435" t="s">
         <v>12</v>
       </c>
       <c r="G435" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="436" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B436" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C436" t="s">
         <v>538</v>
       </c>
       <c r="D436" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E436" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F436" t="s">
         <v>12</v>
       </c>
       <c r="G436" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="437" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B437" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C437" t="s">
         <v>539</v>
       </c>
       <c r="D437" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="E437" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F437" t="s">
         <v>12</v>
       </c>
       <c r="G437" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
     </row>
     <row r="438" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B438" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C438" t="s">
         <v>540</v>
       </c>
       <c r="D438" t="s">
-        <v>535</v>
+        <v>402</v>
       </c>
       <c r="E438" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F438" t="s">
         <v>12</v>
       </c>
       <c r="G438" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
     </row>
     <row r="439" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B439" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C439" t="s">
         <v>541</v>
       </c>
       <c r="D439" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E439" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F439" t="s">
         <v>12</v>
       </c>
       <c r="G439" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="440" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B440" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C440" t="s">
         <v>542</v>
       </c>
       <c r="D440" t="s">
-        <v>404</v>
+        <v>531</v>
       </c>
       <c r="E440" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F440" t="s">
         <v>12</v>
       </c>
       <c r="G440" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="441" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B441" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C441" t="s">
         <v>543</v>
       </c>
       <c r="D441" t="s">
-        <v>531</v>
+        <v>130</v>
       </c>
       <c r="E441" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F441" t="s">
         <v>12</v>
       </c>
       <c r="G441" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="442" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B442" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C442" t="s">
         <v>544</v>
       </c>
       <c r="D442" t="s">
-        <v>533</v>
+        <v>408</v>
       </c>
       <c r="E442" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F442" t="s">
         <v>12</v>
       </c>
       <c r="G442" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="443" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B443" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C443" t="s">
         <v>545</v>
       </c>
       <c r="D443" t="s">
-        <v>130</v>
+        <v>546</v>
       </c>
       <c r="E443" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F443" t="s">
         <v>12</v>
       </c>
       <c r="G443" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="444" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B444" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C444" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D444" t="s">
-        <v>410</v>
+        <v>511</v>
       </c>
       <c r="E444" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F444" t="s">
         <v>12</v>
       </c>
       <c r="G444" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="445" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B445" t="s">
+        <v>524</v>
+      </c>
+      <c r="C445" t="s">
+        <v>548</v>
+      </c>
+      <c r="D445" t="s">
         <v>526</v>
       </c>
-      <c r="C445" t="s">
-        <v>547</v>
-      </c>
-      <c r="D445" t="s">
-        <v>548</v>
-      </c>
       <c r="E445" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F445" t="s">
         <v>12</v>
       </c>
       <c r="G445" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
     </row>
     <row r="446" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B446" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C446" t="s">
         <v>549</v>
       </c>
       <c r="D446" t="s">
-        <v>513</v>
+        <v>402</v>
       </c>
       <c r="E446" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F446" t="s">
         <v>12</v>
       </c>
       <c r="G446" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
     </row>
     <row r="447" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B447" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C447" t="s">
         <v>550</v>
       </c>
       <c r="D447" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E447" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F447" t="s">
         <v>12</v>
       </c>
       <c r="G447" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="448" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B448" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C448" t="s">
         <v>551</v>
       </c>
       <c r="D448" t="s">
-        <v>404</v>
+        <v>531</v>
       </c>
       <c r="E448" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F448" t="s">
         <v>12</v>
       </c>
       <c r="G448" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="449" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B449" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C449" t="s">
         <v>552</v>
       </c>
       <c r="D449" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E449" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F449" t="s">
         <v>12</v>
       </c>
       <c r="G449" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="450" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B450" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C450" t="s">
         <v>553</v>
       </c>
       <c r="D450" t="s">
-        <v>533</v>
+        <v>130</v>
       </c>
       <c r="E450" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F450" t="s">
         <v>12</v>
       </c>
       <c r="G450" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="451" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B451" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C451" t="s">
         <v>554</v>
       </c>
       <c r="D451" t="s">
-        <v>535</v>
+        <v>408</v>
       </c>
       <c r="E451" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F451" t="s">
         <v>12</v>
       </c>
       <c r="G451" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="452" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B452" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C452" t="s">
         <v>555</v>
       </c>
       <c r="D452" t="s">
-        <v>130</v>
+        <v>546</v>
       </c>
       <c r="E452" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F452" t="s">
         <v>12</v>
       </c>
       <c r="G452" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="453" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B453" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C453" t="s">
         <v>556</v>
       </c>
       <c r="D453" t="s">
-        <v>410</v>
+        <v>526</v>
       </c>
       <c r="E453" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F453" t="s">
         <v>12</v>
       </c>
       <c r="G453" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
     </row>
     <row r="454" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B454" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C454" t="s">
         <v>557</v>
       </c>
       <c r="D454" t="s">
-        <v>548</v>
+        <v>402</v>
       </c>
       <c r="E454" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F454" t="s">
         <v>12</v>
       </c>
       <c r="G454" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
     </row>
     <row r="455" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B455" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C455" t="s">
         <v>558</v>
       </c>
       <c r="D455" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E455" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F455" t="s">
         <v>12</v>
       </c>
       <c r="G455" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="456" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B456" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C456" t="s">
         <v>559</v>
       </c>
       <c r="D456" t="s">
-        <v>404</v>
+        <v>531</v>
       </c>
       <c r="E456" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F456" t="s">
         <v>12</v>
       </c>
       <c r="G456" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="457" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B457" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C457" t="s">
         <v>560</v>
       </c>
       <c r="D457" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E457" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F457" t="s">
         <v>12</v>
       </c>
       <c r="G457" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="458" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B458" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C458" t="s">
         <v>561</v>
       </c>
       <c r="D458" t="s">
-        <v>533</v>
+        <v>408</v>
       </c>
       <c r="E458" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F458" t="s">
         <v>12</v>
       </c>
       <c r="G458" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="459" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B459" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C459" t="s">
         <v>562</v>
       </c>
       <c r="D459" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="E459" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F459" t="s">
         <v>12</v>
       </c>
       <c r="G459" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="460" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B460" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C460" t="s">
         <v>563</v>
       </c>
       <c r="D460" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E460" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F460" t="s">
         <v>12</v>
       </c>
       <c r="G460" t="s">
-        <v>323</v>
+        <v>166</v>
       </c>
     </row>
     <row r="461" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B461" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C461" t="s">
         <v>564</v>
       </c>
       <c r="D461" t="s">
-        <v>548</v>
+        <v>130</v>
       </c>
       <c r="E461" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F461" t="s">
         <v>12</v>
       </c>
       <c r="G461" t="s">
-        <v>323</v>
+        <v>166</v>
       </c>
     </row>
     <row r="462" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B462" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C462" t="s">
         <v>565</v>
       </c>
       <c r="D462" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E462" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F462" t="s">
         <v>12</v>
@@ -12729,19 +12723,19 @@
     </row>
     <row r="463" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B463" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C463" t="s">
         <v>566</v>
       </c>
       <c r="D463" t="s">
-        <v>130</v>
+        <v>546</v>
       </c>
       <c r="E463" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F463" t="s">
         <v>12</v>
@@ -12752,178 +12746,178 @@
     </row>
     <row r="464" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B464" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C464" t="s">
         <v>567</v>
       </c>
       <c r="D464" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E464" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F464" t="s">
         <v>12</v>
       </c>
       <c r="G464" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
     </row>
     <row r="465" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B465" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C465" t="s">
         <v>568</v>
       </c>
       <c r="D465" t="s">
-        <v>548</v>
+        <v>130</v>
       </c>
       <c r="E465" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F465" t="s">
         <v>12</v>
       </c>
       <c r="G465" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
     </row>
     <row r="466" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B466" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C466" t="s">
         <v>569</v>
       </c>
       <c r="D466" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E466" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F466" t="s">
         <v>12</v>
       </c>
       <c r="G466" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="467" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B467" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C467" t="s">
         <v>570</v>
       </c>
       <c r="D467" t="s">
-        <v>130</v>
+        <v>546</v>
       </c>
       <c r="E467" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F467" t="s">
         <v>12</v>
       </c>
       <c r="G467" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="468" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B468" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C468" t="s">
         <v>571</v>
       </c>
       <c r="D468" t="s">
-        <v>410</v>
+        <v>546</v>
       </c>
       <c r="E468" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F468" t="s">
         <v>12</v>
       </c>
       <c r="G468" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="469" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>525</v>
+        <v>572</v>
       </c>
       <c r="B469" t="s">
-        <v>526</v>
+        <v>573</v>
       </c>
       <c r="C469" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D469" t="s">
-        <v>548</v>
+        <v>575</v>
       </c>
       <c r="E469" t="s">
-        <v>405</v>
+        <v>11</v>
       </c>
       <c r="F469" t="s">
         <v>12</v>
       </c>
       <c r="G469" t="s">
-        <v>197</v>
+        <v>237</v>
       </c>
     </row>
     <row r="470" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>525</v>
+        <v>572</v>
       </c>
       <c r="B470" t="s">
-        <v>526</v>
+        <v>573</v>
       </c>
       <c r="C470" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D470" t="s">
-        <v>548</v>
+        <v>575</v>
       </c>
       <c r="E470" t="s">
-        <v>405</v>
+        <v>11</v>
       </c>
       <c r="F470" t="s">
         <v>12</v>
       </c>
       <c r="G470" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
     </row>
     <row r="471" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B471" t="s">
+        <v>573</v>
+      </c>
+      <c r="C471" t="s">
+        <v>577</v>
+      </c>
+      <c r="D471" t="s">
         <v>575</v>
       </c>
-      <c r="C471" t="s">
-        <v>576</v>
-      </c>
-      <c r="D471" t="s">
-        <v>577</v>
-      </c>
       <c r="E471" t="s">
         <v>11</v>
       </c>
@@ -12931,21 +12925,21 @@
         <v>12</v>
       </c>
       <c r="G471" t="s">
-        <v>238</v>
+        <v>277</v>
       </c>
     </row>
     <row r="472" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B472" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C472" t="s">
         <v>578</v>
       </c>
       <c r="D472" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E472" t="s">
         <v>11</v>
@@ -12954,21 +12948,21 @@
         <v>12</v>
       </c>
       <c r="G472" t="s">
-        <v>258</v>
+        <v>296</v>
       </c>
     </row>
     <row r="473" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B473" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C473" t="s">
         <v>579</v>
       </c>
       <c r="D473" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E473" t="s">
         <v>11</v>
@@ -12977,21 +12971,21 @@
         <v>12</v>
       </c>
       <c r="G473" t="s">
-        <v>278</v>
+        <v>322</v>
       </c>
     </row>
     <row r="474" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B474" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C474" t="s">
         <v>580</v>
       </c>
       <c r="D474" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E474" t="s">
         <v>11</v>
@@ -13000,21 +12994,21 @@
         <v>12</v>
       </c>
       <c r="G474" t="s">
-        <v>297</v>
+        <v>104</v>
       </c>
     </row>
     <row r="475" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B475" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C475" t="s">
         <v>581</v>
       </c>
       <c r="D475" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E475" t="s">
         <v>11</v>
@@ -13023,21 +13017,21 @@
         <v>12</v>
       </c>
       <c r="G475" t="s">
-        <v>323</v>
+        <v>166</v>
       </c>
     </row>
     <row r="476" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B476" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C476" t="s">
         <v>582</v>
       </c>
       <c r="D476" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E476" t="s">
         <v>11</v>
@@ -13046,21 +13040,21 @@
         <v>12</v>
       </c>
       <c r="G476" t="s">
-        <v>104</v>
+        <v>196</v>
       </c>
     </row>
     <row r="477" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B477" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C477" t="s">
         <v>583</v>
       </c>
       <c r="D477" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E477" t="s">
         <v>11</v>
@@ -13069,21 +13063,21 @@
         <v>12</v>
       </c>
       <c r="G477" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
     </row>
     <row r="478" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B478" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C478" t="s">
         <v>584</v>
       </c>
       <c r="D478" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E478" t="s">
         <v>11</v>
@@ -13092,21 +13086,21 @@
         <v>12</v>
       </c>
       <c r="G478" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
     </row>
     <row r="479" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B479" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C479" t="s">
         <v>585</v>
       </c>
       <c r="D479" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E479" t="s">
         <v>11</v>
@@ -13115,21 +13109,21 @@
         <v>12</v>
       </c>
       <c r="G479" t="s">
-        <v>209</v>
+        <v>13</v>
       </c>
     </row>
     <row r="480" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B480" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C480" t="s">
         <v>586</v>
       </c>
       <c r="D480" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E480" t="s">
         <v>11</v>
@@ -13138,21 +13132,21 @@
         <v>12</v>
       </c>
       <c r="G480" t="s">
-        <v>221</v>
+        <v>41</v>
       </c>
     </row>
     <row r="481" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B481" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C481" t="s">
         <v>587</v>
       </c>
       <c r="D481" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E481" t="s">
         <v>11</v>
@@ -13161,21 +13155,21 @@
         <v>12</v>
       </c>
       <c r="G481" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
     </row>
     <row r="482" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B482" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C482" t="s">
         <v>588</v>
       </c>
       <c r="D482" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E482" t="s">
         <v>11</v>
@@ -13184,21 +13178,21 @@
         <v>12</v>
       </c>
       <c r="G482" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
     </row>
     <row r="483" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="B483" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="C483" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D483" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="E483" t="s">
         <v>11</v>
@@ -13207,21 +13201,21 @@
         <v>12</v>
       </c>
       <c r="G483" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
     </row>
     <row r="484" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="B484" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="C484" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D484" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
       <c r="E484" t="s">
         <v>11</v>
@@ -13230,52 +13224,6 @@
         <v>12</v>
       </c>
       <c r="G484" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="485" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A485" t="s">
-        <v>591</v>
-      </c>
-      <c r="B485" t="s">
-        <v>591</v>
-      </c>
-      <c r="C485" t="s">
-        <v>592</v>
-      </c>
-      <c r="D485" t="s">
-        <v>593</v>
-      </c>
-      <c r="E485" t="s">
-        <v>11</v>
-      </c>
-      <c r="F485" t="s">
-        <v>12</v>
-      </c>
-      <c r="G485" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="486" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A486" t="s">
-        <v>591</v>
-      </c>
-      <c r="B486" t="s">
-        <v>591</v>
-      </c>
-      <c r="C486" t="s">
-        <v>594</v>
-      </c>
-      <c r="D486" t="s">
-        <v>595</v>
-      </c>
-      <c r="E486" t="s">
-        <v>11</v>
-      </c>
-      <c r="F486" t="s">
-        <v>12</v>
-      </c>
-      <c r="G486" t="s">
         <v>13</v>
       </c>
     </row>
